--- a/U-Pb/U-Pb_Results.xlsx
+++ b/U-Pb/U-Pb_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55fd3f8ffa58db1a/Documents - Zircon Recrystallization/Manuscripts/MZ_Replacement/U-Pb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="8_{0DBB9A1D-8D43-4879-9CE7-36AE49D8818C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BA93F1-2C37-48B6-9A06-2BCD517E1452}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="8_{0DBB9A1D-8D43-4879-9CE7-36AE49D8818C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F338DBBF-93F1-4D06-BF32-CA48C916C2AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{06EC71D9-91BE-467D-ABC4-CB3006456D9B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{06EC71D9-91BE-467D-ABC4-CB3006456D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -59,9 +59,9 @@
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    RPRZC = Run product metamict zircon
-RPHZR = run product replacement zircon
-RPCZ = run product crystalline zircon (zones that were crystalline before the experiment; he may not have analyzed them)
+    RPRZC = Run product recrystallized zircon core (previously metamict)
+RPHZR = run product hydrothermal  zircon rim/replacement
+RPCZ = run product crystalline zircon (zones that were crystalline before the experiment)
 SMMZ = starting material metamict zircon
 SMCZ = starting material crystalline zircon
 </t>
@@ -81,29 +81,6 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Use these values</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={B90B5220-61A2-4F8E-B338-1D68579E34A3}</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{B90B5220-61A2-4F8E-B338-1D68579E34A3}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    RPRZC = Run product metamict zircon
-RPHZR = run product replacement zircon
-RPCZ = run product crystalline zircon (zones that were crystalline before the experiment; he may not have analyzed them)
-SMMZ = starting material metamict zircon
-SMCZ = starting material crystalline zircon
-*Note: analyses 16-2 and 14-2 have been deleted</t>
       </text>
     </comment>
   </commentList>
@@ -866,7 +843,7 @@
     <numFmt numFmtId="175" formatCode="\ \-\-\-"/>
     <numFmt numFmtId="176" formatCode="[&gt;=100]0.0;[&gt;0]0.00;0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -911,12 +888,6 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1162,10 +1133,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <numFmt numFmtId="167" formatCode="0.0"/>
     </dxf>
@@ -1179,28 +1147,7 @@
       <alignment wrapText="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="[&gt;=100]0.0;[&gt;0]0.00;0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="[&gt;=100]0.0;[&gt;0]0.00;0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="0.0"/>
@@ -1230,33 +1177,6 @@
         <extend val="0"/>
         <color indexed="9"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="[&gt;=100]0.0;[&gt;0]0.00;0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="[&gt;=100]0.0;[&gt;0]0.00;0.0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="0.0"/>
@@ -1303,6 +1223,9 @@
       <numFmt numFmtId="167" formatCode="0.0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="0"/>
     </dxf>
     <dxf>
@@ -1334,7 +1257,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Ayers, John C" refreshedDate="46287.606636921293" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="54" xr:uid="{CE238C59-7279-4C05-904B-4B9B04FA7981}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Ayers, John C" refreshedDate="46293.5637712963" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="54" xr:uid="{CE238C59-7279-4C05-904B-4B9B04FA7981}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:BI55" sheet="Data"/>
   </cacheSource>
@@ -4950,7 +4873,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DA81C24-88A7-4D42-9D8B-1BFADE6FF217}" name="PivotTable2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DA81C24-88A7-4D42-9D8B-1BFADE6FF217}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:R9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="61">
     <pivotField axis="axisRow" showAll="0">
@@ -5125,7 +5048,7 @@
     <dataField name="Count of (1) 206Pb/238U Age" fld="21" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="41">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5134,7 +5057,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5143,7 +5066,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -5156,7 +5079,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5165,7 +5088,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5188,7 +5111,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{693555E2-1AD3-427A-B478-F0430DC72D8A}" name="PivotTable1" cacheId="16" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{693555E2-1AD3-427A-B478-F0430DC72D8A}" name="PivotTable1" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A13:G23" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="61">
     <pivotField axis="axisCol" showAll="0">
@@ -5340,7 +5263,7 @@
     <dataField name="Count of (1) 206Pb/238U Age" fld="21" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="45">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5349,7 +5272,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5358,7 +5281,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5367,7 +5290,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="9">
@@ -5384,7 +5307,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="25">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5410,16 +5333,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10040D62-A0DF-433F-B5F6-E4157B03823A}" name="Table1" displayName="Table1" ref="AA1:AI7" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10040D62-A0DF-433F-B5F6-E4157B03823A}" name="Table1" displayName="Table1" ref="AA1:AI7" totalsRowShown="0" headerRowDxfId="19">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EEADEE6C-98DB-4442-8E94-EA834EDCAF4E}" name="Row Labels"/>
-    <tableColumn id="2" xr3:uid="{E693E898-A728-430F-BE29-696D87929F02}" name="Min of % Discordant" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{5049B8CB-10EE-4C35-853F-0B6ABCE8BEC7}" name="Max of % Discordant" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{62A81749-650C-45F2-86D2-EB470AEA0B07}" name="Average of ppm U" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{5FFBB9D2-F129-4D43-A35D-45E2E2850578}" name="Average of ppm Th" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{28ABF310-A808-4DEE-9312-4C3EC62618D7}" name="Average of 207Pb/206Pb Age" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{261914C9-69E7-4D1F-9A21-B56D942A1AE7}" name="Average of 206Pb/238U Age" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{C9E56765-A6E3-4D04-8B29-259B9132CAFE}" name="Average of %206Pbc" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{E693E898-A728-430F-BE29-696D87929F02}" name="Min of % Discordant" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{5049B8CB-10EE-4C35-853F-0B6ABCE8BEC7}" name="Max of % Discordant" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{62A81749-650C-45F2-86D2-EB470AEA0B07}" name="Average of ppm U" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{5FFBB9D2-F129-4D43-A35D-45E2E2850578}" name="Average of ppm Th" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{28ABF310-A808-4DEE-9312-4C3EC62618D7}" name="Average of 207Pb/206Pb Age" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{261914C9-69E7-4D1F-9A21-B56D942A1AE7}" name="Average of 206Pb/238U Age" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{C9E56765-A6E3-4D04-8B29-259B9132CAFE}" name="Average of %206Pbc" dataDxfId="12"/>
     <tableColumn id="9" xr3:uid="{103FBF92-BB02-4D98-BF68-4F48C3C25AA2}" name="Count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -5744,9 +5667,9 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="A1" dT="2026-08-13T17:28:09.72" personId="{D8E9D275-7C4F-440D-B17A-76847E38446C}" id="{B28A1433-DA6B-4145-A923-7AC9247D1E7C}">
-    <text xml:space="preserve">RPRZC = Run product metamict zircon
-RPHZR = run product replacement zircon
-RPCZ = run product crystalline zircon (zones that were crystalline before the experiment; he may not have analyzed them)
+    <text xml:space="preserve">RPRZC = Run product recrystallized zircon core (previously metamict)
+RPHZR = run product hydrothermal  zircon rim/replacement
+RPCZ = run product crystalline zircon (zones that were crystalline before the experiment)
 SMMZ = starting material metamict zircon
 SMCZ = starting material crystalline zircon
 </text>
@@ -5756,19 +5679,6 @@
   </threadedComment>
   <threadedComment ref="AK1" dT="2026-09-22T19:07:42.76" personId="{D8E9D275-7C4F-440D-B17A-76847E38446C}" id="{409E867E-90AD-4005-92BE-69BDC03CD723}">
     <text>Use these values</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A1" dT="2026-08-13T17:28:09.72" personId="{D8E9D275-7C4F-440D-B17A-76847E38446C}" id="{B90B5220-61A2-4F8E-B338-1D68579E34A3}">
-    <text>RPRZC = Run product metamict zircon
-RPHZR = run product replacement zircon
-RPCZ = run product crystalline zircon (zones that were crystalline before the experiment; he may not have analyzed them)
-SMMZ = starting material metamict zircon
-SMCZ = starting material crystalline zircon
-*Note: analyses 16-2 and 14-2 have been deleted</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -16015,7 +15925,7 @@
   </sheetData>
   <autoFilter ref="A1:BI55" xr:uid="{A60B72F6-481B-4C02-82AB-88A004042E7E}"/>
   <conditionalFormatting sqref="F2:BI55">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>ISERROR(F2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16026,7 +15936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF45376-4FCF-48C3-B5D5-24383A976B9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF45376-4FCF-48C3-B5D5-24383A976B9B}">
   <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17750,12 +17660,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:J55">
-    <cfRule type="expression" dxfId="18" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="1" stopIfTrue="1">
       <formula>ISERROR(E2)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17768,7 +17677,8 @@
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
